--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118555513</v>
+        <v>118553786</v>
       </c>
       <c r="B5" t="n">
-        <v>5166</v>
+        <v>97750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Saxberget (Saxberget), Dlr</t>
+          <t>Långfallsgruvan (Långfallsgruvan), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497255</v>
+        <v>497118</v>
       </c>
       <c r="R5" t="n">
-        <v>6666074</v>
+        <v>6666332</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118553786</v>
+        <v>118555513</v>
       </c>
       <c r="B6" t="n">
-        <v>97750</v>
+        <v>5166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långfallsgruvan (Långfallsgruvan), Dlr</t>
+          <t>Saxberget (Saxberget), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497118</v>
+        <v>497255</v>
       </c>
       <c r="R6" t="n">
-        <v>6666332</v>
+        <v>6666074</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118563956</v>
+        <v>118563958</v>
       </c>
       <c r="B2" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Saxberget, Ludvika, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497273</v>
+        <v>497266</v>
       </c>
       <c r="R2" t="n">
-        <v>6666171</v>
+        <v>6666251</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118563955</v>
+        <v>118563956</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Saxberget, Ludvika, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497222</v>
+        <v>497273</v>
       </c>
       <c r="R3" t="n">
-        <v>6666142</v>
+        <v>6666171</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118563958</v>
+        <v>118563955</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497266</v>
+        <v>497222</v>
       </c>
       <c r="R4" t="n">
-        <v>6666251</v>
+        <v>6666142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118563956</v>
+        <v>118563955</v>
       </c>
       <c r="B3" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Saxberget, Ludvika, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497273</v>
+        <v>497222</v>
       </c>
       <c r="R3" t="n">
-        <v>6666171</v>
+        <v>6666142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118563955</v>
+        <v>118563956</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>90511</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Saxberget, Ludvika, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497222</v>
+        <v>497273</v>
       </c>
       <c r="R4" t="n">
-        <v>6666142</v>
+        <v>6666171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118553786</v>
+        <v>118555513</v>
       </c>
       <c r="B5" t="n">
-        <v>97750</v>
+        <v>5166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långfallsgruvan (Långfallsgruvan), Dlr</t>
+          <t>Saxberget (Saxberget), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497118</v>
+        <v>497255</v>
       </c>
       <c r="R5" t="n">
-        <v>6666332</v>
+        <v>6666074</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118555513</v>
+        <v>118553786</v>
       </c>
       <c r="B6" t="n">
-        <v>5166</v>
+        <v>97757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Saxberget (Saxberget), Dlr</t>
+          <t>Långfallsgruvan (Långfallsgruvan), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497255</v>
+        <v>497118</v>
       </c>
       <c r="R6" t="n">
-        <v>6666074</v>
+        <v>6666332</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118563958</v>
+        <v>118563955</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497266</v>
+        <v>497222</v>
       </c>
       <c r="R2" t="n">
-        <v>6666251</v>
+        <v>6666142</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118563955</v>
+        <v>118563958</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497222</v>
+        <v>497266</v>
       </c>
       <c r="R3" t="n">
-        <v>6666142</v>
+        <v>6666251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118555513</v>
+        <v>118553786</v>
       </c>
       <c r="B5" t="n">
-        <v>5166</v>
+        <v>97757</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Saxberget (Saxberget), Dlr</t>
+          <t>Långfallsgruvan (Långfallsgruvan), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497255</v>
+        <v>497118</v>
       </c>
       <c r="R5" t="n">
-        <v>6666074</v>
+        <v>6666332</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118553786</v>
+        <v>118555513</v>
       </c>
       <c r="B6" t="n">
-        <v>97757</v>
+        <v>5166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långfallsgruvan (Långfallsgruvan), Dlr</t>
+          <t>Saxberget (Saxberget), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497118</v>
+        <v>497255</v>
       </c>
       <c r="R6" t="n">
-        <v>6666332</v>
+        <v>6666074</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1193,117 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122031240</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98131</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Saxdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497049</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6666280</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>122031240</v>
       </c>
       <c r="B7" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>122031240</v>
       </c>
       <c r="B7" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>122031240</v>
       </c>
       <c r="B7" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>122031240</v>
       </c>
       <c r="B7" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>122031240</v>
       </c>
       <c r="B7" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>122031240</v>
       </c>
       <c r="B7" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>122031240</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>122031240</v>
       </c>
       <c r="B7" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 54639-2020 artfynd.xlsx
+++ b/artfynd/A 54639-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118563955</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>118563958</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
